--- a/Lucknow-December-2025.xlsx
+++ b/Lucknow-December-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Lucknow</t>
   </si>
   <si>
@@ -109,7 +112,7 @@
     <t>HR55AX2090</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>DZIRE</t>
@@ -480,10 +483,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,28 +565,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>286</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2">
         <v>143593</v>
@@ -612,6 +618,12 @@
       <c r="P2">
         <v>132662</v>
       </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
       <c r="S2">
         <v>132662</v>
       </c>
@@ -637,27 +649,27 @@
         <v>64.59</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>287</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H3">
         <v>125986</v>
@@ -686,6 +698,12 @@
       <c r="P3">
         <v>76110</v>
       </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
       <c r="S3">
         <v>76110</v>
       </c>
@@ -711,24 +729,24 @@
         <v>62.68</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>288</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2">
         <v>45997</v>
@@ -759,6 +777,12 @@
       </c>
       <c r="P4">
         <v>26520</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
       </c>
       <c r="S4">
         <v>26520</v>
